--- a/AutoAvaliacao/AutoAvaliacaoM3P2-JoaoLuizi.xlsx
+++ b/AutoAvaliacao/AutoAvaliacaoM3P2-JoaoLuizi.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2025_repos\M3_Project2_JML\AutoAvaliacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F1462C-78F9-4AB0-961B-418810652B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB875AC-3E1A-4A5F-ADB5-855DB96B159F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>Projecto 1</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>Lucas Lemos</t>
+  </si>
+  <si>
+    <t>Apesar de inicialmente ter sido construída a maioria da estrutura do projeto, houve um contratempo com o Github em que me levou a perder uma grande parte do trabalho que já tinha feito, como já estávamos perto da data de entrega, levou a que fosse mais recorrente a utilização de LLM's para acelerar o processo de reconstrução da informação que foi perdida.</t>
   </si>
 </sst>
 </file>
@@ -144,7 +147,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -441,15 +444,55 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -459,10 +502,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -479,7 +519,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -489,50 +528,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -828,25 +831,25 @@
   </cols>
   <sheetData>
     <row r="3" spans="4:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="26"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="41"/>
     </row>
     <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
     </row>
     <row r="6" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="4" t="s">
@@ -858,11 +861,11 @@
       <c r="F6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
     </row>
     <row r="7" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D7" s="3">
@@ -874,9 +877,9 @@
       <c r="F7" s="12">
         <v>1</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
     </row>
     <row r="8" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D8" s="1">
@@ -888,9 +891,9 @@
       <c r="F8" s="13">
         <v>1</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D9" s="1">
@@ -902,11 +905,11 @@
       <c r="F9" s="13">
         <v>1</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
     </row>
     <row r="10" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D10" s="1">
@@ -914,9 +917,9 @@
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
     </row>
     <row r="11" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D11" s="1">
@@ -924,9 +927,9 @@
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
     </row>
     <row r="12" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D12" s="1">
@@ -934,9 +937,9 @@
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="13"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
     </row>
     <row r="13" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D13" s="1">
@@ -944,9 +947,9 @@
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="13"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="20"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="36"/>
     </row>
     <row r="14" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D14" s="1">
@@ -954,9 +957,9 @@
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="20"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="36"/>
     </row>
     <row r="15" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D15" s="1">
@@ -964,9 +967,9 @@
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="13"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="20"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="36"/>
     </row>
     <row r="16" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D16" s="1">
@@ -974,46 +977,46 @@
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="13"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="20"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="36"/>
     </row>
     <row r="17" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
       <c r="E17" s="10"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="20"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="36"/>
     </row>
     <row r="18" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D18" s="7"/>
       <c r="E18" s="11"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
     </row>
     <row r="19" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="17"/>
+      <c r="E19" s="47"/>
       <c r="F19" s="8"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
     </row>
     <row r="20" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="23"/>
     </row>
     <row r="22" spans="4:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="6" t="s">
@@ -1042,7 +1045,7 @@
       <c r="E23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="49">
+      <c r="F23" s="15">
         <v>30</v>
       </c>
       <c r="G23" s="14">
@@ -1051,7 +1054,7 @@
       <c r="H23" s="14">
         <v>0.95</v>
       </c>
-      <c r="I23" s="48" t="s">
+      <c r="I23" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1060,19 +1063,25 @@
       <c r="E24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="50">
+      <c r="F24" s="16">
         <v>30</v>
       </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
+      <c r="G24" s="50">
+        <v>0.8</v>
+      </c>
+      <c r="H24" s="50">
+        <v>0.75</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="25" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="50">
+      <c r="F25" s="16">
         <v>30</v>
       </c>
       <c r="G25" s="2"/>
@@ -1084,7 +1093,7 @@
       <c r="E26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="50">
+      <c r="F26" s="16">
         <v>10</v>
       </c>
       <c r="G26" s="2"/>
@@ -1101,14 +1110,14 @@
     </row>
     <row r="28" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D29" s="33" t="s">
+      <c r="D29" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="36"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="23"/>
     </row>
     <row r="30" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D30" s="6" t="s">
@@ -1117,12 +1126,12 @@
       <c r="E30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="40" t="s">
+      <c r="F30" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D31" s="5">
@@ -1131,12 +1140,12 @@
       <c r="E31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="42" t="s">
+      <c r="F31" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="44"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="28"/>
     </row>
     <row r="32" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D32" s="2">
@@ -1145,12 +1154,12 @@
       <c r="E32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="39"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="19"/>
     </row>
     <row r="33" spans="4:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="2">
@@ -1159,12 +1168,12 @@
       <c r="E33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="45" t="s">
+      <c r="F33" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="47"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="31"/>
     </row>
     <row r="34" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D34" s="2">
@@ -1173,12 +1182,12 @@
       <c r="E34" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="F34" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="39"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="19"/>
     </row>
     <row r="35" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D35" s="2">
@@ -1187,12 +1196,12 @@
       <c r="E35" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="39"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="19"/>
     </row>
     <row r="36" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D36" s="2">
@@ -1201,12 +1210,12 @@
       <c r="E36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F36" s="45" t="s">
+      <c r="F36" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="47"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="31"/>
     </row>
     <row r="37" spans="4:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="2">
@@ -1215,12 +1224,12 @@
       <c r="E37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="39"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="19"/>
     </row>
     <row r="38" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D38" s="2">
@@ -1229,25 +1238,43 @@
       <c r="E38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F38" s="45" t="s">
+      <c r="F38" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="47"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="31"/>
     </row>
     <row r="39" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D39" s="2">
         <v>9</v>
       </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="39"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G19:I19"/>
     <mergeCell ref="F34:I34"/>
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="F39:I39"/>
@@ -1259,24 +1286,6 @@
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="F37:I37"/>
     <mergeCell ref="F38:I38"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G18:I18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/AutoAvaliacao/AutoAvaliacaoM3P2-JoaoLuizi.xlsx
+++ b/AutoAvaliacao/AutoAvaliacaoM3P2-JoaoLuizi.xlsx
@@ -1,31 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2025_repos\M3_Project2_JML\AutoAvaliacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB875AC-3E1A-4A5F-ADB5-855DB96B159F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6992ED5-F938-4BA6-9B74-A31F42E70A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+  <si>
+    <t>MÓDULO III</t>
+  </si>
   <si>
     <t>Projecto 1</t>
   </si>
@@ -42,6 +56,18 @@
     <t>Obs</t>
   </si>
   <si>
+    <t>Expandir a base de dados do Módulo II – Projeto II e garantir a correta implementação das regras de negócio descritas no enunciado, através do desenvolvimento de uma solução baseada em Web API.</t>
+  </si>
+  <si>
+    <t>Implementar um sistema de autenticação utilizando JWT Bearer e garantir a restrição de acesso a endpoints específicos, de acordo com as regras de negócio e perfis de administrador.</t>
+  </si>
+  <si>
+    <t>Utilizar um sistema de controlo de versões (Git) para garantir a sincronização, gestão e colaboração eficiente entre os vários elementos da equipa.</t>
+  </si>
+  <si>
+    <t>No âmbito deste projeto, foram utilizadas apenas funcionalidades básicas do Git, nomeadamente criação e gestão de branches, checkout, operações de sincronização (push/pull), bem como staging, commit e merge.</t>
+  </si>
+  <si>
     <t>Final</t>
   </si>
   <si>
@@ -60,86 +86,74 @@
     <t>% Avaliação Global</t>
   </si>
   <si>
-    <t>Ficheiros</t>
-  </si>
-  <si>
-    <t>Pasta</t>
-  </si>
-  <si>
-    <t>MÓDULO III</t>
-  </si>
-  <si>
-    <t>AutoAvaliação</t>
-  </si>
-  <si>
-    <t>DalPro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contém os itens da autoavaliação (incluindo este documento) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projeto :  Business Layer (modelos, DTOs, repositórios e interfaces) </t>
-  </si>
-  <si>
-    <t>Projecto: Web API (endpoints e service layer)</t>
-  </si>
-  <si>
-    <t>Projecto: Data Access Layer (wrapper sobre métodos ADO.NET)</t>
-  </si>
-  <si>
-    <t>Scripts de criação da base de dados e seed de dados</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Documentação geral do projeto    </t>
-  </si>
-  <si>
-    <t>DBTools</t>
-  </si>
-  <si>
-    <t>Docs</t>
-  </si>
-  <si>
-    <t>XPTOBusiness</t>
-  </si>
-  <si>
-    <t>XPTOWebAPI</t>
-  </si>
-  <si>
-    <t>README.md</t>
-  </si>
-  <si>
-    <t>Documentação especifica do Projecto : Subject</t>
-  </si>
-  <si>
-    <t>Expandir a base de dados do Módulo II – Projeto II e garantir a correta implementação das regras de negócio descritas no enunciado, através do desenvolvimento de uma solução baseada em Web API.</t>
-  </si>
-  <si>
-    <t>Implementar um sistema de autenticação utilizando JWT Bearer e garantir a restrição de acesso a endpoints específicos, de acordo com as regras de negócio e perfis de administrador.</t>
-  </si>
-  <si>
-    <t>Utilizar um sistema de controlo de versões (Git) para garantir a sincronização, gestão e colaboração eficiente entre os vários elementos da equipa.</t>
-  </si>
-  <si>
-    <t>No âmbito deste projeto, foram utilizadas apenas funcionalidades básicas do Git, nomeadamente criação e gestão de branches, checkout, operações de sincronização (push/pull), bem como staging, commit e merge.</t>
-  </si>
-  <si>
-    <t>LLM's</t>
+    <t>João Luizi</t>
   </si>
   <si>
     <t>O projeto foi desenvolvido de forma autónoma, com recurso a materiais online e adaptação de templates fornecidos nas aulas. As regras de negócio foram implementadas através da replicação de lógica existente em stored procedures (SPs) do Projeto do Módulo II ou pela sua invocação direta.
 Modelos de linguagem (LLMs) foram utilizados como ferramenta de produtividade, sobretudo na aceleração de tarefas repetitivas, dado que o desenvolvimento assentou maioritariamente em lógica previamente implementada.</t>
   </si>
   <si>
-    <t>João Luizi</t>
-  </si>
-  <si>
     <t>Luís Silva</t>
   </si>
   <si>
+    <t>Apesar de inicialmente ter sido construída a maioria da estrutura do projeto, houve um contratempo com o Github em que me levou a perder uma grande parte do trabalho que já tinha feito, como já estávamos perto da data de entrega, levou a que fosse mais recorrente a utilização de LLM's para acelerar o processo de reconstrução da informação que foi perdida.</t>
+  </si>
+  <si>
     <t>Lucas Lemos</t>
   </si>
   <si>
-    <t>Apesar de inicialmente ter sido construída a maioria da estrutura do projeto, houve um contratempo com o Github em que me levou a perder uma grande parte do trabalho que já tinha feito, como já estávamos perto da data de entrega, levou a que fosse mais recorrente a utilização de LLM's para acelerar o processo de reconstrução da informação que foi perdida.</t>
+    <t>Tendo o projeto grande base em lógicas previsamente implementadas, o trabalho desenvolvido foi autónomo, tendo usado modelos de linguagem sobretudo para aceleração de processos. A adaptação do modelo SQL do módulo 2 para C# foi bem conseguida.</t>
+  </si>
+  <si>
+    <t>LLM's</t>
+  </si>
+  <si>
+    <t>Ficheiros</t>
+  </si>
+  <si>
+    <t>Pasta</t>
+  </si>
+  <si>
+    <t>AutoAvaliação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contém os itens da autoavaliação (incluindo este documento) </t>
+  </si>
+  <si>
+    <t>XPTOBusiness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projeto :  Business Layer (modelos, DTOs, repositórios e interfaces) </t>
+  </si>
+  <si>
+    <t>DBTools</t>
+  </si>
+  <si>
+    <t>Scripts de criação da base de dados e seed de dados</t>
+  </si>
+  <si>
+    <t>Docs</t>
+  </si>
+  <si>
+    <t>Documentação especifica do Projecto : Subject</t>
+  </si>
+  <si>
+    <t>DalPro</t>
+  </si>
+  <si>
+    <t>Projecto: Data Access Layer (wrapper sobre métodos ADO.NET)</t>
+  </si>
+  <si>
+    <t>XPTOWebAPI</t>
+  </si>
+  <si>
+    <t>Projecto: Web API (endpoints e service layer)</t>
+  </si>
+  <si>
+    <t>README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Documentação geral do projeto    </t>
   </si>
 </sst>
 </file>
@@ -149,7 +163,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -408,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -446,6 +460,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -461,8 +479,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -502,7 +518,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -512,7 +527,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -534,8 +548,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -817,7 +834,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="D3:I39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="2" width="3.5703125" customWidth="1"/>
@@ -830,63 +847,63 @@
     <col min="9" max="9" width="44.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="41"/>
-    </row>
-    <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="42" t="s">
+    <row r="3" spans="4:9" ht="35.25" customHeight="1">
+      <c r="D3" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-    </row>
-    <row r="6" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="47"/>
+    </row>
+    <row r="4" spans="4:9" ht="15.75" thickBot="1"/>
+    <row r="5" spans="4:9" ht="19.5" thickBot="1">
+      <c r="D5" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+    </row>
+    <row r="6" spans="4:9" ht="16.5" thickBot="1">
       <c r="D6" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-    </row>
-    <row r="7" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+    </row>
+    <row r="7" spans="4:9" ht="15.75">
       <c r="D7" s="3">
         <v>1</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F7" s="12">
         <v>1</v>
       </c>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-    </row>
-    <row r="8" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="43"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+    </row>
+    <row r="8" spans="4:9" ht="15.75">
       <c r="D8" s="1">
         <v>2</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F8" s="13">
         <v>1</v>
@@ -895,23 +912,23 @@
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
     </row>
-    <row r="9" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:9" ht="15.75">
       <c r="D9" s="1">
         <v>3</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F9" s="13">
         <v>1</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
     </row>
-    <row r="10" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:9" ht="15.75">
       <c r="D10" s="1">
         <v>4</v>
       </c>
@@ -921,7 +938,7 @@
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
     </row>
-    <row r="11" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:9" ht="15.75">
       <c r="D11" s="1">
         <v>5</v>
       </c>
@@ -931,7 +948,7 @@
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
     </row>
-    <row r="12" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:9" ht="15.75">
       <c r="D12" s="1">
         <v>6</v>
       </c>
@@ -941,7 +958,7 @@
       <c r="H12" s="33"/>
       <c r="I12" s="33"/>
     </row>
-    <row r="13" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:9" ht="15.75">
       <c r="D13" s="1">
         <v>7</v>
       </c>
@@ -951,7 +968,7 @@
       <c r="H13" s="35"/>
       <c r="I13" s="36"/>
     </row>
-    <row r="14" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:9" ht="15.75">
       <c r="D14" s="1">
         <v>8</v>
       </c>
@@ -961,7 +978,7 @@
       <c r="H14" s="35"/>
       <c r="I14" s="36"/>
     </row>
-    <row r="15" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:9" ht="15.75">
       <c r="D15" s="1">
         <v>9</v>
       </c>
@@ -971,7 +988,7 @@
       <c r="H15" s="35"/>
       <c r="I15" s="36"/>
     </row>
-    <row r="16" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="4:9" ht="15.75">
       <c r="D16" s="1">
         <v>10</v>
       </c>
@@ -981,7 +998,7 @@
       <c r="H16" s="35"/>
       <c r="I16" s="36"/>
     </row>
-    <row r="17" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:9" ht="15.75">
       <c r="D17" s="1"/>
       <c r="E17" s="10"/>
       <c r="F17" s="1"/>
@@ -989,61 +1006,61 @@
       <c r="H17" s="35"/>
       <c r="I17" s="36"/>
     </row>
-    <row r="18" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:9" ht="16.5" thickBot="1">
       <c r="D18" s="7"/>
       <c r="E18" s="11"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="48"/>
+      <c r="G18" s="46"/>
       <c r="H18" s="49"/>
       <c r="I18" s="49"/>
     </row>
-    <row r="19" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D19" s="47" t="s">
+    <row r="19" spans="4:9" ht="19.5" thickBot="1">
+      <c r="D19" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="45"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+    </row>
+    <row r="20" spans="4:9" ht="15.75" thickBot="1"/>
+    <row r="21" spans="4:9" ht="19.5" thickBot="1">
+      <c r="D21" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="51"/>
+    </row>
+    <row r="22" spans="4:9" ht="48" thickBot="1">
+      <c r="D22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-    </row>
-    <row r="20" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D21" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="23"/>
-    </row>
-    <row r="22" spans="4:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D22" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="4:9" ht="183">
       <c r="D23" s="5">
         <v>1</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F23" s="15">
         <v>30</v>
@@ -1054,44 +1071,50 @@
       <c r="H23" s="14">
         <v>0.95</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I23" s="18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="4:9">
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F24" s="16">
         <v>30</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="17">
         <v>0.8</v>
       </c>
-      <c r="H24" s="50">
+      <c r="H24" s="17">
         <v>0.75</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="4:9">
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F25" s="16">
         <v>30</v>
       </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="G25" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="H25" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="4:9">
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F26" s="16">
         <v>10</v>
@@ -1100,7 +1123,7 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:9">
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -1108,152 +1131,152 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D29" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="23"/>
-    </row>
-    <row r="30" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:9" ht="15.75" thickBot="1"/>
+    <row r="29" spans="4:9" ht="19.5" thickBot="1">
+      <c r="D29" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="51"/>
+    </row>
+    <row r="30" spans="4:9" ht="16.5" thickBot="1">
       <c r="D30" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F30" s="24" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="25"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:9">
       <c r="D31" s="5">
         <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="I31" s="28"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:9">
       <c r="D32" s="2">
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="19"/>
-    </row>
-    <row r="33" spans="4:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="21"/>
+    </row>
+    <row r="33" spans="4:9" ht="15" customHeight="1">
       <c r="D33" s="2">
         <v>3</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G33" s="30"/>
       <c r="H33" s="30"/>
       <c r="I33" s="31"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:9">
       <c r="D34" s="2">
         <v>4</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="19"/>
-    </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="21"/>
+    </row>
+    <row r="35" spans="4:9">
       <c r="D35" s="2">
         <v>5</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="19"/>
-    </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="21"/>
+    </row>
+    <row r="36" spans="4:9">
       <c r="D36" s="2">
         <v>6</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G36" s="30"/>
       <c r="H36" s="30"/>
       <c r="I36" s="31"/>
     </row>
-    <row r="37" spans="4:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:9" ht="15" customHeight="1">
       <c r="D37" s="2">
         <v>7</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="19"/>
-    </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="21"/>
+    </row>
+    <row r="38" spans="4:9">
       <c r="D38" s="2">
         <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G38" s="30"/>
       <c r="H38" s="30"/>
       <c r="I38" s="31"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:9">
       <c r="D39" s="2">
         <v>9</v>
       </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="29">

--- a/AutoAvaliacao/AutoAvaliacaoM3P2-JoaoLuizi.xlsx
+++ b/AutoAvaliacao/AutoAvaliacaoM3P2-JoaoLuizi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2025_repos\M3_Project2_JML\AutoAvaliacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB875AC-3E1A-4A5F-ADB5-855DB96B159F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284AD469-8B33-49EF-A79C-043ACCF2AC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t>Projecto 1</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Apesar de inicialmente ter sido construída a maioria da estrutura do projeto, houve um contratempo com o Github em que me levou a perder uma grande parte do trabalho que já tinha feito, como já estávamos perto da data de entrega, levou a que fosse mais recorrente a utilização de LLM's para acelerar o processo de reconstrução da informação que foi perdida.</t>
+  </si>
+  <si>
+    <t>Tendo o projeto grande base em lógicas previsamente implementadas, o trabalho desenvolvido foi autónomo, tendo usado modelos de linguagem sobretudo para aceleração de processos. A adaptação do modelo SQL do módulo 2 para C# foi bem conseguida.</t>
   </si>
 </sst>
 </file>
@@ -446,53 +449,16 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -502,7 +468,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -519,6 +488,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -528,14 +498,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -831,25 +834,25 @@
   </cols>
   <sheetData>
     <row r="3" spans="4:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="41"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
     </row>
     <row r="6" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="4" t="s">
@@ -861,11 +864,11 @@
       <c r="F6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
     </row>
     <row r="7" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D7" s="3">
@@ -877,9 +880,9 @@
       <c r="F7" s="12">
         <v>1</v>
       </c>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
     </row>
     <row r="8" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D8" s="1">
@@ -891,9 +894,9 @@
       <c r="F8" s="13">
         <v>1</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D9" s="1">
@@ -905,11 +908,11 @@
       <c r="F9" s="13">
         <v>1</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D10" s="1">
@@ -917,9 +920,9 @@
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="11" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D11" s="1">
@@ -927,9 +930,9 @@
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
     </row>
     <row r="12" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D12" s="1">
@@ -937,9 +940,9 @@
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="13"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D13" s="1">
@@ -947,9 +950,9 @@
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="13"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="36"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D14" s="1">
@@ -957,9 +960,9 @@
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="36"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D15" s="1">
@@ -967,9 +970,9 @@
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="13"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D16" s="1">
@@ -977,46 +980,46 @@
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="13"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="4:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
       <c r="E17" s="10"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="36"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="23"/>
     </row>
     <row r="18" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D18" s="7"/>
       <c r="E18" s="11"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="47"/>
+      <c r="E19" s="20"/>
       <c r="F19" s="8"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
     </row>
     <row r="20" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="23"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39"/>
     </row>
     <row r="22" spans="4:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="6" t="s">
@@ -1066,10 +1069,10 @@
       <c r="F24" s="16">
         <v>30</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="17">
         <v>0.8</v>
       </c>
-      <c r="H24" s="50">
+      <c r="H24" s="17">
         <v>0.75</v>
       </c>
       <c r="I24" s="2" t="s">
@@ -1084,9 +1087,15 @@
       <c r="F25" s="16">
         <v>30</v>
       </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="G25" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="H25" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="26" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D26" s="2"/>
@@ -1110,14 +1119,14 @@
     </row>
     <row r="28" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="23"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39"/>
     </row>
     <row r="30" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D30" s="6" t="s">
@@ -1126,12 +1135,12 @@
       <c r="E30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="24" t="s">
+      <c r="F30" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
     </row>
     <row r="31" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D31" s="5">
@@ -1140,12 +1149,12 @@
       <c r="E31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F31" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="28"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="47"/>
     </row>
     <row r="32" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D32" s="2">
@@ -1154,12 +1163,12 @@
       <c r="E32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="19"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="42"/>
     </row>
     <row r="33" spans="4:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="2">
@@ -1168,12 +1177,12 @@
       <c r="E33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F33" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="31"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="50"/>
     </row>
     <row r="34" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D34" s="2">
@@ -1182,12 +1191,12 @@
       <c r="E34" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="19"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="42"/>
     </row>
     <row r="35" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D35" s="2">
@@ -1196,12 +1205,12 @@
       <c r="E35" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="19"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="42"/>
     </row>
     <row r="36" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D36" s="2">
@@ -1210,12 +1219,12 @@
       <c r="E36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="31"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="50"/>
     </row>
     <row r="37" spans="4:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="2">
@@ -1224,12 +1233,12 @@
       <c r="E37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="19"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="42"/>
     </row>
     <row r="38" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D38" s="2">
@@ -1238,43 +1247,25 @@
       <c r="E38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="31"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="50"/>
     </row>
     <row r="39" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D39" s="2">
         <v>9</v>
       </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="19"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G19:I19"/>
     <mergeCell ref="F34:I34"/>
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="F39:I39"/>
@@ -1286,6 +1277,24 @@
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="F37:I37"/>
     <mergeCell ref="F38:I38"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G18:I18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
